--- a/doc-engine-core/src/test/resources/templates/table-each.xlsx
+++ b/doc-engine-core/src/test/resources/templates/table-each.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>Name</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>${item.qty * item.price}</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -74,7 +77,7 @@
       <patternFill patternType="darkGray"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,12 +85,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -102,32 +124,35 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="1">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="1">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="B3" t="s" s="1">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1">
         <f>SUM(C2:C2)</f>
       </c>
     </row>
